--- a/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -440,12 +440,13 @@
   <x:dimension ref="A1:G14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="7" width="10.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23.567768" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">

--- a/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -446,7 +446,7 @@
     <x:col min="4" max="4" width="20.282054" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="23.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.567768" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
